--- a/Software.xlsx
+++ b/Software.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA57526-8A42-4FE1-B52E-F87C749B28B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D947B7B8-F07E-4562-AEDC-BBF0A0BCCE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52390" yWindow="1580" windowWidth="21660" windowHeight="13240" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14235" yWindow="90" windowWidth="26190" windowHeight="20805" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acquisitions" sheetId="18" r:id="rId1"/>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="772">
   <si>
     <t>Name</t>
   </si>
@@ -2476,13 +2476,17 @@
   </si>
   <si>
     <t>Cisco</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="164" formatCode="0\x"/>
     <numFmt numFmtId="165" formatCode="[$¥-411]#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
@@ -3382,7 +3386,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="120" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="342">
+  <cellXfs count="343">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="119" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="119" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4059,6 +4063,9 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="123" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="113" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4210,27 +4217,27 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Model"/>
+      <sheetName val="Models"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>1178</v>
+            <v>2358.9073969999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>17787</v>
+            <v>5430.6890000000003</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>9592</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4244,27 +4251,27 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Models"/>
+      <sheetName val="Model"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>2358.9073969999999</v>
+            <v>1178</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>5430.6890000000003</v>
+            <v>17787</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>0</v>
+            <v>9592</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4284,37 +4291,21 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="M3">
-            <v>973</v>
+            <v>920</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>17653</v>
+            <v>17799</v>
           </cell>
         </row>
         <row r="6">
           <cell r="M6">
-            <v>0</v>
+            <v>56531</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1">
-        <row r="62">
-          <cell r="AE62">
-            <v>0.01</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="AE63">
-            <v>0.08</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="AE65">
-            <v>170.42672158668651</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4334,21 +4325,37 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="M3">
-            <v>920</v>
+            <v>973</v>
           </cell>
         </row>
         <row r="5">
           <cell r="M5">
-            <v>17799</v>
+            <v>17653</v>
           </cell>
         </row>
         <row r="6">
           <cell r="M6">
-            <v>56531</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1">
+        <row r="62">
+          <cell r="AE62">
+            <v>0.01</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="AE63">
+            <v>0.08</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="AE65">
+            <v>170.42672158668651</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4401,18 +4408,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="P3">
-            <v>265</v>
+          <cell r="M3">
+            <v>331</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="P5">
-            <v>7373</v>
+          <cell r="M5">
+            <v>5027.4579999999996</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="P6">
-            <v>2982</v>
+          <cell r="M6">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -4435,18 +4442,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>260</v>
+          <cell r="P3">
+            <v>265</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="L5">
-            <v>2562</v>
+          <cell r="P5">
+            <v>7373</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="L6">
-            <v>986</v>
+          <cell r="P6">
+            <v>2982</v>
           </cell>
         </row>
       </sheetData>
@@ -4469,18 +4476,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="M3">
-            <v>331</v>
+          <cell r="L3">
+            <v>260</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="M5">
-            <v>5027.4579999999996</v>
+          <cell r="L5">
+            <v>2562</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="M6">
-            <v>0</v>
+          <cell r="L6">
+            <v>986</v>
           </cell>
         </row>
       </sheetData>
@@ -4668,7 +4675,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>74</v>
+            <v>81.36</v>
           </cell>
         </row>
         <row r="5">
@@ -4682,7 +4689,18 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1">
+        <row r="44">
+          <cell r="AC44">
+            <v>0.11</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="AC47">
+            <v>607.75128881946102</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -6979,24 +6997,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024DBDC7-DC6F-4550-A83F-1B2B66C2DF19}">
   <dimension ref="A1:X13"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="121" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" style="121" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.1796875" style="121"/>
+    <col min="1" max="1" width="5.42578125" style="121" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="121" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="121"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="121" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D2" s="121" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B3" s="121" t="s">
         <v>449</v>
       </c>
@@ -7004,7 +7022,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B4" s="121" t="s">
         <v>450</v>
       </c>
@@ -7012,7 +7030,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B5" s="121" t="s">
         <v>409</v>
       </c>
@@ -7020,7 +7038,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="121" t="s">
         <v>452</v>
       </c>
@@ -7028,7 +7046,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B7" s="121" t="s">
         <v>453</v>
       </c>
@@ -7036,7 +7054,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B8" s="121" t="s">
         <v>454</v>
       </c>
@@ -7047,7 +7065,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B9" s="121" t="s">
         <v>456</v>
       </c>
@@ -7055,7 +7073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B10" s="124" t="s">
         <v>477</v>
       </c>
@@ -7066,7 +7084,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="66"/>
       <c r="B11" s="5" t="s">
         <v>168</v>
@@ -7100,7 +7118,7 @@
         <v>44946</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="54" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="125" t="s">
         <v>251</v>
       </c>
@@ -7120,7 +7138,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="54" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="83" t="s">
         <v>184</v>
       </c>
@@ -7145,24 +7163,24 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDDC990C-C1C5-4FE2-B554-717099EBE596}">
   <dimension ref="A1:AA45"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7265625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" style="10" customWidth="1"/>
-    <col min="6" max="9" width="9.1796875" style="10"/>
-    <col min="10" max="10" width="10.26953125" style="10" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="10"/>
+    <col min="5" max="5" width="9.85546875" style="10" customWidth="1"/>
+    <col min="6" max="9" width="9.140625" style="10"/>
+    <col min="10" max="10" width="10.28515625" style="10" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
@@ -7236,7 +7254,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="264" t="s">
         <v>251</v>
       </c>
@@ -7279,7 +7297,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="262" t="s">
         <v>251</v>
       </c>
@@ -7310,7 +7328,7 @@
       </c>
       <c r="M4" s="135"/>
     </row>
-    <row r="5" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="264" t="s">
         <v>251</v>
       </c>
@@ -7371,7 +7389,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="64"/>
       <c r="B6" s="5" t="s">
         <v>257</v>
@@ -7418,7 +7436,7 @@
       <c r="V6" s="24"/>
       <c r="W6" s="24"/>
     </row>
-    <row r="7" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="97"/>
       <c r="B7" s="5" t="s">
         <v>257</v>
@@ -7465,7 +7483,7 @@
       <c r="V7" s="24"/>
       <c r="W7" s="24"/>
     </row>
-    <row r="8" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="264" t="s">
         <v>251</v>
       </c>
@@ -7503,7 +7521,7 @@
       <c r="V8" s="24"/>
       <c r="W8" s="24"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="264" t="s">
         <v>251</v>
       </c>
@@ -7525,7 +7543,7 @@
         <v>50938.435697071494</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="264" t="s">
         <v>251</v>
       </c>
@@ -7546,7 +7564,7 @@
         <v>52220</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="264" t="s">
         <v>251</v>
       </c>
@@ -7567,7 +7585,7 @@
         <v>56400</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="264" t="s">
         <v>251</v>
       </c>
@@ -7606,7 +7624,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="264" t="s">
         <v>251</v>
       </c>
@@ -7652,7 +7670,7 @@
         <v>612.81624321428569</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="66"/>
       <c r="B14" s="5" t="s">
         <v>647</v>
@@ -7686,7 +7704,7 @@
         <v>45587</v>
       </c>
     </row>
-    <row r="15" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="264" t="s">
         <v>251</v>
       </c>
@@ -7703,7 +7721,7 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="264" t="s">
         <v>251</v>
       </c>
@@ -7739,7 +7757,7 @@
         <v>45735</v>
       </c>
     </row>
-    <row r="17" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>251</v>
       </c>
@@ -7759,7 +7777,7 @@
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
         <v>727</v>
       </c>
@@ -7772,7 +7790,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
         <v>462</v>
       </c>
@@ -7785,7 +7803,7 @@
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>468</v>
       </c>
@@ -7795,7 +7813,7 @@
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>470</v>
       </c>
@@ -7808,7 +7826,7 @@
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="264" t="s">
         <v>251</v>
       </c>
@@ -7824,7 +7842,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>249</v>
       </c>
@@ -7837,7 +7855,7 @@
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="264" t="s">
         <v>251</v>
       </c>
@@ -7881,7 +7899,7 @@
       <c r="V24" s="24"/>
       <c r="W24" s="26"/>
     </row>
-    <row r="25" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="5" t="s">
         <v>649</v>
       </c>
@@ -7914,7 +7932,7 @@
         <v>45629</v>
       </c>
     </row>
-    <row r="26" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="51" t="s">
         <v>248</v>
       </c>
@@ -7939,7 +7957,7 @@
       <c r="V26" s="24"/>
       <c r="W26" s="24"/>
     </row>
-    <row r="27" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="123" t="s">
         <v>474</v>
       </c>
@@ -7967,7 +7985,7 @@
       <c r="V27" s="24"/>
       <c r="W27" s="24"/>
     </row>
-    <row r="28" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D28" s="21"/>
       <c r="E28" s="22"/>
       <c r="F28" s="23"/>
@@ -7989,7 +8007,7 @@
       <c r="V28" s="24"/>
       <c r="W28" s="24"/>
     </row>
-    <row r="29" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D29" s="21"/>
       <c r="E29" s="22"/>
       <c r="F29" s="23"/>
@@ -8011,7 +8029,7 @@
       <c r="V29" s="24"/>
       <c r="W29" s="24"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B30" s="1" t="s">
         <v>54</v>
       </c>
@@ -8032,7 +8050,7 @@
         <v>116.66666666666667</v>
       </c>
     </row>
-    <row r="31" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="s">
         <v>57</v>
       </c>
@@ -8059,7 +8077,7 @@
       <c r="V31" s="24"/>
       <c r="W31" s="24"/>
     </row>
-    <row r="32" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
         <v>108</v>
       </c>
@@ -8086,22 +8104,22 @@
       <c r="V32" s="24"/>
       <c r="W32" s="24"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B33" s="49" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B34" s="103" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B35" s="122" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B36" s="118" t="s">
         <v>439</v>
       </c>
@@ -8112,7 +8130,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B37" s="122" t="s">
         <v>459</v>
       </c>
@@ -8121,26 +8139,26 @@
         <v>460</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B38" s="122" t="s">
         <v>464</v>
       </c>
       <c r="H38" s="118"/>
       <c r="J38" s="122"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B39" s="122" t="s">
         <v>465</v>
       </c>
       <c r="H39" s="118"/>
       <c r="J39" s="122"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B40" s="122" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B41" s="122" t="s">
         <v>472</v>
       </c>
@@ -8148,20 +8166,20 @@
         <v>473</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B42" s="122" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B43" s="122" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B44" s="122"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B45" s="122" t="s">
         <v>457</v>
       </c>
@@ -8189,26 +8207,26 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E275841C-1187-4786-8CDA-18459BF1140B}">
   <dimension ref="A1:Z60"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="163" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" style="163" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" style="163" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="164"/>
-    <col min="5" max="5" width="9.1796875" style="162"/>
-    <col min="6" max="7" width="9.1796875" style="164"/>
-    <col min="8" max="8" width="9.1796875" style="162"/>
-    <col min="9" max="9" width="9.1796875" style="164"/>
-    <col min="10" max="10" width="10.453125" style="163" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="163"/>
+    <col min="2" max="2" width="18.28515625" style="163" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="163" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="164"/>
+    <col min="5" max="5" width="9.140625" style="162"/>
+    <col min="6" max="7" width="9.140625" style="164"/>
+    <col min="8" max="8" width="9.140625" style="162"/>
+    <col min="9" max="9" width="9.140625" style="164"/>
+    <col min="10" max="10" width="10.42578125" style="163" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="163"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B2" s="165" t="s">
         <v>0</v>
       </c>
@@ -8285,7 +8303,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="265" t="s">
         <v>251</v>
       </c>
@@ -8335,7 +8353,7 @@
         <v>12.76</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="265" t="s">
         <v>251</v>
       </c>
@@ -8381,7 +8399,7 @@
         <v>18.690000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="265" t="s">
         <v>251</v>
       </c>
@@ -8443,7 +8461,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="265" t="s">
         <v>251</v>
       </c>
@@ -8498,7 +8516,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="265" t="s">
         <v>251</v>
       </c>
@@ -8541,7 +8559,7 @@
         <v>10.89</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="265" t="s">
         <v>251</v>
       </c>
@@ -8580,7 +8598,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9" s="265" t="s">
         <v>251</v>
       </c>
@@ -8619,7 +8637,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="265" t="s">
         <v>251</v>
       </c>
@@ -8671,7 +8689,7 @@
         <v>5.64</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="265" t="s">
         <v>251</v>
       </c>
@@ -8717,7 +8735,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="265" t="s">
         <v>251</v>
       </c>
@@ -8760,7 +8778,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="265" t="s">
         <v>251</v>
       </c>
@@ -8803,7 +8821,7 @@
         <v>19.149999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="265" t="s">
         <v>251</v>
       </c>
@@ -8855,7 +8873,7 @@
         <v>1.62</v>
       </c>
     </row>
-    <row r="15" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="265" t="s">
         <v>251</v>
       </c>
@@ -8876,7 +8894,7 @@
       <c r="X15" s="310"/>
       <c r="Y15" s="310"/>
     </row>
-    <row r="16" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="313" t="s">
         <v>251</v>
       </c>
@@ -8897,7 +8915,7 @@
       <c r="X16" s="310"/>
       <c r="Y16" s="310"/>
     </row>
-    <row r="17" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="265" t="s">
         <v>251</v>
       </c>
@@ -8918,7 +8936,7 @@
       <c r="X17" s="310"/>
       <c r="Y17" s="310"/>
     </row>
-    <row r="18" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="265" t="s">
         <v>251</v>
       </c>
@@ -8939,7 +8957,7 @@
       <c r="X18" s="310"/>
       <c r="Y18" s="310"/>
     </row>
-    <row r="19" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="265" t="s">
         <v>251</v>
       </c>
@@ -8960,7 +8978,7 @@
       <c r="X19" s="310"/>
       <c r="Y19" s="310"/>
     </row>
-    <row r="20" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="265" t="s">
         <v>251</v>
       </c>
@@ -8983,7 +9001,7 @@
       <c r="X20" s="310"/>
       <c r="Y20" s="310"/>
     </row>
-    <row r="21" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="265" t="s">
         <v>251</v>
       </c>
@@ -9004,7 +9022,7 @@
       <c r="X21" s="310"/>
       <c r="Y21" s="310"/>
     </row>
-    <row r="22" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="265" t="s">
         <v>251</v>
       </c>
@@ -9023,7 +9041,7 @@
       <c r="O22" s="163"/>
       <c r="P22" s="163"/>
     </row>
-    <row r="23" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="265" t="s">
         <v>251</v>
       </c>
@@ -9044,7 +9062,7 @@
       <c r="O23" s="163"/>
       <c r="P23" s="163"/>
     </row>
-    <row r="24" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="265" t="s">
         <v>251</v>
       </c>
@@ -9065,7 +9083,7 @@
       <c r="O24" s="163"/>
       <c r="P24" s="163"/>
     </row>
-    <row r="25" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="265" t="s">
         <v>251</v>
       </c>
@@ -9086,7 +9104,7 @@
       <c r="O25" s="163"/>
       <c r="P25" s="163"/>
     </row>
-    <row r="26" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="265" t="s">
         <v>251</v>
       </c>
@@ -9109,7 +9127,7 @@
       <c r="O26" s="163"/>
       <c r="P26" s="163"/>
     </row>
-    <row r="27" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="265" t="s">
         <v>251</v>
       </c>
@@ -9128,7 +9146,7 @@
       <c r="O27" s="163"/>
       <c r="P27" s="163"/>
     </row>
-    <row r="28" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="329" t="s">
         <v>251</v>
       </c>
@@ -9147,7 +9165,7 @@
       <c r="O28" s="163"/>
       <c r="P28" s="163"/>
     </row>
-    <row r="29" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="174" t="s">
         <v>251</v>
       </c>
@@ -9170,7 +9188,7 @@
       <c r="O29" s="163"/>
       <c r="P29" s="163"/>
     </row>
-    <row r="30" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="174" t="s">
         <v>251</v>
       </c>
@@ -9193,7 +9211,7 @@
       <c r="O30" s="163"/>
       <c r="P30" s="163"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A31" s="265" t="s">
         <v>251</v>
       </c>
@@ -9226,7 +9244,7 @@
       <c r="X31" s="178"/>
       <c r="Y31" s="178"/>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A32" s="316" t="s">
         <v>251</v>
       </c>
@@ -9254,7 +9272,7 @@
       <c r="X32" s="178"/>
       <c r="Y32" s="178"/>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A33" s="316" t="s">
         <v>251</v>
       </c>
@@ -9282,7 +9300,7 @@
       <c r="X33" s="178"/>
       <c r="Y33" s="178"/>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A34" s="163" t="s">
         <v>251</v>
       </c>
@@ -9299,7 +9317,7 @@
         <v>19090</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B35" s="190" t="s">
         <v>639</v>
       </c>
@@ -9313,7 +9331,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A36" s="163" t="s">
         <v>251</v>
       </c>
@@ -9324,7 +9342,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A37" s="163" t="s">
         <v>251</v>
       </c>
@@ -9335,7 +9353,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A38" s="163" t="s">
         <v>251</v>
       </c>
@@ -9346,7 +9364,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A39" s="163" t="s">
         <v>251</v>
       </c>
@@ -9357,7 +9375,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A40" s="163" t="s">
         <v>251</v>
       </c>
@@ -9368,7 +9386,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A41" s="265" t="s">
         <v>251</v>
       </c>
@@ -9379,7 +9397,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A42" s="163" t="s">
         <v>251</v>
       </c>
@@ -9390,7 +9408,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B43" s="5" t="s">
         <v>645</v>
       </c>
@@ -9401,7 +9419,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A44" s="265" t="s">
         <v>251</v>
       </c>
@@ -9412,7 +9430,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A45" s="163" t="s">
         <v>251</v>
       </c>
@@ -9423,7 +9441,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A46" s="163" t="s">
         <v>251</v>
       </c>
@@ -9434,7 +9452,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A47" s="163" t="s">
         <v>251</v>
       </c>
@@ -9445,7 +9463,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B48" s="5" t="s">
         <v>655</v>
       </c>
@@ -9456,7 +9474,7 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B49" s="5" t="s">
         <v>656</v>
       </c>
@@ -9464,7 +9482,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="163" t="s">
         <v>251</v>
       </c>
@@ -9475,7 +9493,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="163" t="s">
         <v>251</v>
       </c>
@@ -9486,7 +9504,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="174" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" s="174" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="47" t="s">
         <v>33</v>
       </c>
@@ -9504,7 +9522,7 @@
       <c r="H53" s="162"/>
       <c r="I53" s="162"/>
     </row>
-    <row r="54" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B54" s="104" t="s">
         <v>58</v>
       </c>
@@ -9516,7 +9534,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B55" s="174" t="s">
         <v>86</v>
       </c>
@@ -9528,7 +9546,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B56" s="163" t="s">
         <v>240</v>
       </c>
@@ -9539,7 +9557,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B57" s="163" t="s">
         <v>242</v>
       </c>
@@ -9547,7 +9565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B58" s="163" t="s">
         <v>272</v>
       </c>
@@ -9555,7 +9573,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B59" s="163" t="s">
         <v>274</v>
       </c>
@@ -9563,7 +9581,7 @@
         <v>159.5</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B60" s="163" t="s">
         <v>397</v>
       </c>
@@ -9590,19 +9608,19 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B3EDE09-CAB5-40D0-A45D-B13186189FA6}">
   <dimension ref="A1:X6"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="251" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.453125" style="251" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.1796875" style="251"/>
+    <col min="1" max="1" width="5.42578125" style="251" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="251" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="251"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B2" s="252" t="s">
         <v>0</v>
       </c>
@@ -9673,7 +9691,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B3" s="250" t="s">
         <v>143</v>
       </c>
@@ -9687,7 +9705,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B4" s="80" t="s">
         <v>667</v>
       </c>
@@ -9699,7 +9717,7 @@
       </c>
       <c r="E4" s="249"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="251" t="s">
         <v>251</v>
       </c>
@@ -9712,7 +9730,7 @@
       <c r="D5" s="261"/>
       <c r="E5" s="249"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="251" t="s">
         <v>251</v>
       </c>
@@ -9735,25 +9753,25 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569EF4EB-ECD2-418F-8A42-9502B535E912}">
   <dimension ref="A1:X49"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" style="10" customWidth="1"/>
-    <col min="3" max="4" width="9.1796875" style="10"/>
+    <col min="2" max="2" width="12.85546875" style="10" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="10"/>
     <col min="5" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="10"/>
+    <col min="6" max="6" width="9.140625" style="10"/>
     <col min="7" max="7" width="10" style="10" customWidth="1"/>
-    <col min="8" max="9" width="9.1796875" style="10"/>
-    <col min="10" max="10" width="10.453125" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="10"/>
+    <col min="8" max="9" width="9.140625" style="10"/>
+    <col min="10" max="10" width="10.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="54" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
@@ -9824,7 +9842,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="266" t="s">
         <v>251</v>
       </c>
@@ -9860,7 +9878,7 @@
         <v>45689</v>
       </c>
     </row>
-    <row r="4" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="266" t="s">
         <v>251</v>
       </c>
@@ -9909,7 +9927,7 @@
       <c r="V4" s="24"/>
       <c r="W4" s="26"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="266" t="s">
         <v>251</v>
       </c>
@@ -9945,7 +9963,7 @@
         <v>45853</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="266" t="s">
         <v>251</v>
       </c>
@@ -9994,7 +10012,7 @@
       <c r="V6" s="24"/>
       <c r="W6" s="26"/>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="266" t="s">
         <v>251</v>
       </c>
@@ -10030,7 +10048,7 @@
         <v>45756</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="266" t="s">
         <v>251</v>
       </c>
@@ -10047,7 +10065,7 @@
         <v>101795</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="266" t="s">
         <v>251</v>
       </c>
@@ -10058,7 +10076,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="266" t="s">
         <v>251</v>
       </c>
@@ -10072,7 +10090,7 @@
         <v>119.23</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="266" t="s">
         <v>251</v>
       </c>
@@ -10108,7 +10126,7 @@
         <v>44971</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="266" t="s">
         <v>251</v>
       </c>
@@ -10119,7 +10137,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="266" t="s">
         <v>251</v>
       </c>
@@ -10130,7 +10148,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="266" t="s">
         <v>251</v>
       </c>
@@ -10166,7 +10184,7 @@
         <v>45712</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="266" t="s">
         <v>251</v>
       </c>
@@ -10197,7 +10215,7 @@
       <c r="V15" s="24"/>
       <c r="W15" s="24"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="266" t="s">
         <v>251</v>
       </c>
@@ -10214,7 +10232,7 @@
         <v>25171</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="266" t="s">
         <v>251</v>
       </c>
@@ -10225,7 +10243,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="266" t="s">
         <v>251</v>
       </c>
@@ -10236,7 +10254,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="266" t="s">
         <v>251</v>
       </c>
@@ -10247,7 +10265,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="266" t="s">
         <v>251</v>
       </c>
@@ -10258,7 +10276,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="324" t="s">
         <v>251</v>
       </c>
@@ -10269,7 +10287,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="324" t="s">
         <v>251</v>
       </c>
@@ -10280,7 +10298,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B23" s="5" t="s">
         <v>505</v>
       </c>
@@ -10291,7 +10309,7 @@
         <v>305.11</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="77"/>
       <c r="B24" s="77" t="s">
         <v>302</v>
@@ -10300,7 +10318,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="77"/>
       <c r="B25" s="5" t="s">
         <v>734</v>
@@ -10312,7 +10330,7 @@
         <v>37.72</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="78"/>
       <c r="B26" s="78" t="s">
         <v>306</v>
@@ -10321,7 +10339,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="79"/>
       <c r="B27" s="79" t="s">
         <v>308</v>
@@ -10330,7 +10348,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="266" t="s">
         <v>251</v>
       </c>
@@ -10341,7 +10359,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="266" t="s">
         <v>251</v>
       </c>
@@ -10358,7 +10376,7 @@
         <v>12580</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="315" t="s">
         <v>251</v>
       </c>
@@ -10371,7 +10389,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B31" s="10" t="s">
         <v>159</v>
       </c>
@@ -10379,7 +10397,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B32" s="5" t="s">
         <v>740</v>
       </c>
@@ -10390,7 +10408,7 @@
         <v>65.05</v>
       </c>
     </row>
-    <row r="33" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="s">
         <v>131</v>
       </c>
@@ -10422,7 +10440,7 @@
       <c r="V33" s="24"/>
       <c r="W33" s="26"/>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
         <v>373</v>
       </c>
@@ -10455,7 +10473,7 @@
         <v>44965</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B35" s="5" t="s">
         <v>624</v>
       </c>
@@ -10488,7 +10506,7 @@
         <v>45556</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" ht="15" x14ac:dyDescent="0.25">
       <c r="B36" s="337" t="s">
         <v>375</v>
       </c>
@@ -10502,7 +10520,7 @@
       <c r="F36" s="44"/>
       <c r="G36" s="44"/>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B37" s="5" t="s">
         <v>643</v>
       </c>
@@ -10535,7 +10553,7 @@
         <v>45583</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B38" s="128" t="s">
         <v>548</v>
       </c>
@@ -10543,7 +10561,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" s="266" t="s">
         <v>251</v>
       </c>
@@ -10554,7 +10572,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="331" t="s">
         <v>251</v>
       </c>
@@ -10565,7 +10583,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B41" s="128" t="s">
         <v>556</v>
       </c>
@@ -10573,7 +10591,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B42" s="129" t="s">
         <v>609</v>
       </c>
@@ -10581,7 +10599,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B43" s="333" t="s">
         <v>736</v>
       </c>
@@ -10592,7 +10610,7 @@
         <v>27.72</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B44" s="5" t="s">
         <v>641</v>
       </c>
@@ -10603,7 +10621,7 @@
         <v>41.16</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B46" s="1" t="s">
         <v>115</v>
       </c>
@@ -10613,7 +10631,7 @@
         <v>8333</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B47" s="20" t="s">
         <v>63</v>
       </c>
@@ -10623,7 +10641,7 @@
         <v>22000</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B48" s="20" t="s">
         <v>55</v>
       </c>
@@ -10633,7 +10651,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B49" s="120" t="s">
         <v>446</v>
       </c>
@@ -10668,24 +10686,24 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2707CF4-895A-4CDE-92B2-BF34D258BE21}">
   <dimension ref="A1:AD23"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="280" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" style="280" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="9.1796875" style="280"/>
-    <col min="10" max="10" width="9.1796875" style="281"/>
-    <col min="11" max="24" width="9.1796875" style="280"/>
-    <col min="25" max="27" width="9.1796875" style="293"/>
-    <col min="28" max="30" width="9.1796875" style="281"/>
-    <col min="31" max="16384" width="9.1796875" style="280"/>
+    <col min="3" max="9" width="9.140625" style="280"/>
+    <col min="10" max="10" width="9.140625" style="281"/>
+    <col min="11" max="24" width="9.140625" style="280"/>
+    <col min="25" max="27" width="9.140625" style="293"/>
+    <col min="28" max="30" width="9.140625" style="281"/>
+    <col min="31" max="16384" width="9.140625" style="280"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B2" s="282" t="s">
         <v>0</v>
       </c>
@@ -10774,7 +10792,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="50" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="50" t="s">
         <v>703</v>
       </c>
@@ -10814,7 +10832,7 @@
         <v>9.8948530840896094</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="291" t="s">
         <v>251</v>
       </c>
@@ -10859,7 +10877,7 @@
         <v>10.133483754512635</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="291" t="s">
         <v>251</v>
       </c>
@@ -10904,7 +10922,7 @@
         <v>9.8652217741935484</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="291" t="s">
         <v>251</v>
       </c>
@@ -10961,7 +10979,7 @@
         <v>14.988191488616462</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="291" t="s">
         <v>251</v>
       </c>
@@ -11006,7 +11024,7 @@
         <v>9.6640891218872866</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="291" t="s">
         <v>251</v>
       </c>
@@ -11063,7 +11081,7 @@
         <v>18.706107856390975</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="291" t="s">
         <v>251</v>
       </c>
@@ -11120,7 +11138,7 @@
         <v>9.2520947514534893</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="291" t="s">
         <v>251</v>
       </c>
@@ -11145,7 +11163,7 @@
       </c>
       <c r="H10" s="281"/>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>191</v>
       </c>
@@ -11199,7 +11217,7 @@
         <v>3.2214258690206896</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="280" t="s">
         <v>251</v>
       </c>
@@ -11210,7 +11228,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="280" t="s">
         <v>251</v>
       </c>
@@ -11221,7 +11239,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="280" t="s">
         <v>251</v>
       </c>
@@ -11232,7 +11250,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="280" t="s">
         <v>251</v>
       </c>
@@ -11243,7 +11261,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="280" t="s">
         <v>251</v>
       </c>
@@ -11300,7 +11318,7 @@
         <v>3.3282100566417907</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="280" t="s">
         <v>251</v>
       </c>
@@ -11311,7 +11329,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="280" t="s">
         <v>251</v>
       </c>
@@ -11322,7 +11340,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="280" t="s">
         <v>251</v>
       </c>
@@ -11333,7 +11351,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B20" s="280" t="s">
         <v>689</v>
       </c>
@@ -11342,7 +11360,7 @@
       </c>
       <c r="D20" s="296"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" s="333" t="s">
         <v>730</v>
       </c>
@@ -11350,7 +11368,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B23" s="280" t="s">
         <v>652</v>
       </c>
@@ -11378,18 +11396,18 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E750321-4AE5-45B4-8FB8-F8D64CF71E0E}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="38" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.1796875" style="38"/>
+    <col min="2" max="16384" width="9.140625" style="38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2" s="38" t="s">
         <v>146</v>
       </c>
@@ -11397,7 +11415,7 @@
         <v>7.8498000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B3" s="38" t="s">
         <v>147</v>
       </c>
@@ -11405,7 +11423,7 @@
         <v>6.74</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" s="38" t="s">
         <v>205</v>
       </c>
@@ -11413,7 +11431,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5" s="38" t="s">
         <v>223</v>
       </c>
@@ -11421,7 +11439,7 @@
         <v>10.54</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B6" s="39" t="s">
         <v>231</v>
       </c>
@@ -11429,7 +11447,7 @@
         <v>136.93</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B7" s="39" t="s">
         <v>232</v>
       </c>
@@ -11449,20 +11467,20 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC5831F-FB2E-134D-9E1A-7188BFBB74B9}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" style="7"/>
-    <col min="4" max="16384" width="9.1796875" style="6"/>
+    <col min="2" max="2" width="19.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="7"/>
+    <col min="4" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
@@ -11482,7 +11500,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8" t="s">
         <v>33</v>
       </c>
@@ -11493,7 +11511,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="6" t="s">
         <v>86</v>
       </c>
@@ -11504,7 +11522,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5" s="6" t="s">
         <v>120</v>
       </c>
@@ -11515,7 +11533,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6" s="6" t="s">
         <v>140</v>
       </c>
@@ -11523,7 +11541,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
         <v>141</v>
       </c>
@@ -11531,7 +11549,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="12" t="s">
         <v>199</v>
       </c>
@@ -11539,7 +11557,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="39" t="s">
         <v>233</v>
       </c>
@@ -11556,7 +11574,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10" s="45" t="s">
         <v>236</v>
       </c>
@@ -11570,7 +11588,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" s="102" t="s">
         <v>385</v>
       </c>
@@ -11590,18 +11608,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29F2F021-B9D2-4E87-AC34-DE48FE1C4298}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="125" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.81640625" style="125"/>
+    <col min="2" max="16384" width="8.85546875" style="125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B2" s="125" t="s">
         <v>222</v>
       </c>
@@ -11612,7 +11630,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" s="125" t="s">
         <v>478</v>
       </c>
@@ -11631,24 +11649,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B21A44C1-F876-4F6A-A905-60D0CF343544}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="87" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.1796875" style="87"/>
+    <col min="2" max="16384" width="9.140625" style="87"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="87" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B3" s="87" t="s">
         <v>334</v>
       </c>
@@ -11656,7 +11674,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" s="87" t="s">
         <v>336</v>
       </c>
@@ -11664,42 +11682,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5" s="87" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B6" s="87" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B7" s="87" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B8" s="87" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B9" s="87" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B10" s="87" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" s="87" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B12" s="87" t="s">
         <v>332</v>
       </c>
@@ -11716,21 +11734,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFCBFEC-29DF-40E8-ABA2-B3BB501AC0C1}">
   <dimension ref="A1:AL135"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="109" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="109" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="109" customWidth="1"/>
     <col min="3" max="7" width="7" style="109" customWidth="1"/>
-    <col min="8" max="17" width="8.08984375" style="109" customWidth="1"/>
-    <col min="18" max="16384" width="9.1796875" style="109"/>
+    <col min="8" max="17" width="8.140625" style="109" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="109"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B2" s="109" t="s">
         <v>0</v>
       </c>
@@ -11872,7 +11890,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B3" s="333" t="s">
         <v>765</v>
       </c>
@@ -12020,7 +12038,7 @@
         <v>59262.727114046538</v>
       </c>
     </row>
-    <row r="4" spans="1:38" s="50" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="50" t="s">
         <v>412</v>
       </c>
@@ -12169,7 +12187,7 @@
         <v>1380922.1133198179</v>
       </c>
     </row>
-    <row r="5" spans="1:38" s="50" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="50" t="s">
         <v>767</v>
       </c>
@@ -12315,7 +12333,7 @@
         <v>0.11187243847503447</v>
       </c>
     </row>
-    <row r="6" spans="1:38" s="50" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C6" s="338"/>
       <c r="D6" s="338"/>
       <c r="E6" s="338"/>
@@ -12353,7 +12371,7 @@
       <c r="AK6" s="340"/>
       <c r="AL6" s="340"/>
     </row>
-    <row r="7" spans="1:38" s="50" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B7" s="50" t="s">
         <v>766</v>
       </c>
@@ -12502,7 +12520,7 @@
         <v>2.3301697045806549E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="110"/>
       <c r="D8" s="110"/>
       <c r="E8" s="110"/>
@@ -12535,7 +12553,7 @@
       <c r="AF8" s="110"/>
       <c r="AG8" s="110"/>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" s="109">
         <v>1</v>
       </c>
@@ -12661,7 +12679,7 @@
         <v>364491.07336350734</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" s="109">
         <f>+A9+1</f>
         <v>2</v>
@@ -12790,7 +12808,7 @@
         <v>244693.80628875003</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" s="109">
         <f>+A10+1</f>
         <v>3</v>
@@ -12916,7 +12934,7 @@
         <v>63519.193269984396</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" s="109">
         <f t="shared" ref="A12:A76" si="17">+A11+1</f>
         <v>4</v>
@@ -13038,7 +13056,7 @@
         <v>22376.618550000003</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" s="109">
         <f t="shared" si="17"/>
         <v>5</v>
@@ -13180,7 +13198,7 @@
         <v>28044.643927859994</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" s="109">
         <f t="shared" si="17"/>
         <v>6</v>
@@ -13310,7 +13328,7 @@
         <v>20961.725596874996</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" s="109">
         <f t="shared" si="17"/>
         <v>7</v>
@@ -13432,7 +13450,7 @@
         <v>26200.753353254306</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" s="109">
         <f t="shared" si="17"/>
         <v>8</v>
@@ -13557,7 +13575,7 @@
         <v>18184</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" s="109">
         <f t="shared" si="17"/>
         <v>9</v>
@@ -13681,7 +13699,7 @@
         <v>28409.396400000009</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" s="109">
         <f t="shared" si="17"/>
         <v>10</v>
@@ -13803,7 +13821,7 @@
         <v>270000</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" s="109">
         <f t="shared" si="17"/>
         <v>11</v>
@@ -13925,7 +13943,7 @@
         <v>7121.3094000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" s="109">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -14066,7 +14084,7 @@
         <v>7262.2821879473158</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" s="109">
         <f t="shared" si="17"/>
         <v>13</v>
@@ -14188,7 +14206,7 @@
         <v>6117.4764000000005</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" s="109">
         <f t="shared" si="17"/>
         <v>14</v>
@@ -14310,7 +14328,7 @@
         <v>6131</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" s="109">
         <f t="shared" si="17"/>
         <v>15</v>
@@ -14432,7 +14450,7 @@
         <v>5089</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" s="109">
         <f t="shared" si="17"/>
         <v>16</v>
@@ -14554,7 +14572,7 @@
         <v>3005.0036100000002</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" s="109">
         <f t="shared" si="17"/>
         <v>17</v>
@@ -14684,7 +14702,7 @@
         <v>2930.6018700000004</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" s="109">
         <f t="shared" si="17"/>
         <v>18</v>
@@ -14806,7 +14824,7 @@
         <v>2754.6358500000001</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" s="109">
         <f t="shared" si="17"/>
         <v>19</v>
@@ -14928,7 +14946,7 @@
         <v>96000</v>
       </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" s="109">
         <f t="shared" si="17"/>
         <v>20</v>
@@ -15050,7 +15068,7 @@
         <v>13463.084180000003</v>
       </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" s="109">
         <f t="shared" si="17"/>
         <v>21</v>
@@ -15173,7 +15191,7 @@
         <v>1535.5101960000002</v>
       </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" s="109">
         <f t="shared" si="17"/>
         <v>22</v>
@@ -15240,7 +15258,7 @@
       <c r="AK30" s="110"/>
       <c r="AL30" s="110"/>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A31" s="109">
         <f t="shared" si="17"/>
         <v>23</v>
@@ -15362,7 +15380,7 @@
         <v>1671.0867000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A32" s="109">
         <f t="shared" si="17"/>
         <v>24</v>
@@ -15482,7 +15500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A33" s="109">
         <f t="shared" si="17"/>
         <v>25</v>
@@ -15599,7 +15617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A34" s="109">
         <f t="shared" si="17"/>
         <v>26</v>
@@ -15721,7 +15739,7 @@
         <v>2063.5078522540002</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A35" s="109">
         <f t="shared" si="17"/>
         <v>27</v>
@@ -15843,7 +15861,7 @@
         <v>894.95958535960017</v>
       </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A36" s="109">
         <f t="shared" si="17"/>
         <v>28</v>
@@ -15953,7 +15971,7 @@
       <c r="AI36" s="110"/>
       <c r="AJ36" s="110"/>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A37" s="109">
         <f t="shared" si="17"/>
         <v>29</v>
@@ -15996,7 +16014,7 @@
       <c r="AI37" s="110"/>
       <c r="AJ37" s="110"/>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A38" s="109">
         <f t="shared" si="17"/>
         <v>30</v>
@@ -16039,7 +16057,7 @@
       <c r="AI38" s="110"/>
       <c r="AJ38" s="110"/>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A39" s="109">
         <f t="shared" si="17"/>
         <v>31</v>
@@ -16161,7 +16179,7 @@
         <v>2203.7281099999996</v>
       </c>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A40" s="109">
         <f t="shared" si="17"/>
         <v>32</v>
@@ -16283,7 +16301,7 @@
         <v>797.71662802590004</v>
       </c>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A41" s="109">
         <f t="shared" si="17"/>
         <v>33</v>
@@ -16326,7 +16344,7 @@
       <c r="AI41" s="110"/>
       <c r="AJ41" s="110"/>
     </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A42" s="109">
         <f t="shared" si="17"/>
         <v>34</v>
@@ -16369,7 +16387,7 @@
       <c r="AI42" s="110"/>
       <c r="AJ42" s="110"/>
     </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A43" s="109">
         <f t="shared" si="17"/>
         <v>35</v>
@@ -16412,7 +16430,7 @@
       <c r="AI43" s="110"/>
       <c r="AJ43" s="110"/>
     </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A44" s="109">
         <f t="shared" si="17"/>
         <v>36</v>
@@ -16455,7 +16473,7 @@
       <c r="AI44" s="110"/>
       <c r="AJ44" s="110"/>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A45" s="109">
         <f t="shared" si="17"/>
         <v>37</v>
@@ -16516,7 +16534,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A46" s="109">
         <f t="shared" si="17"/>
         <v>38</v>
@@ -16559,7 +16577,7 @@
       <c r="AI46" s="110"/>
       <c r="AJ46" s="110"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A47" s="109">
         <f t="shared" si="17"/>
         <v>39</v>
@@ -16602,7 +16620,7 @@
       <c r="AI47" s="110"/>
       <c r="AJ47" s="110"/>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A48" s="109">
         <f t="shared" si="17"/>
         <v>40</v>
@@ -16645,7 +16663,7 @@
       <c r="AI48" s="110"/>
       <c r="AJ48" s="110"/>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A49" s="109">
         <f t="shared" si="17"/>
         <v>41</v>
@@ -16688,7 +16706,7 @@
       <c r="AI49" s="110"/>
       <c r="AJ49" s="110"/>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A50" s="109">
         <f t="shared" si="17"/>
         <v>42</v>
@@ -16731,7 +16749,7 @@
       <c r="AI50" s="110"/>
       <c r="AJ50" s="110"/>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A51" s="109">
         <f t="shared" si="17"/>
         <v>43</v>
@@ -16774,7 +16792,7 @@
       <c r="AI51" s="110"/>
       <c r="AJ51" s="110"/>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A52" s="109">
         <f t="shared" si="17"/>
         <v>44</v>
@@ -16817,7 +16835,7 @@
       <c r="AI52" s="110"/>
       <c r="AJ52" s="110"/>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A53" s="109">
         <f t="shared" si="17"/>
         <v>45</v>
@@ -16860,7 +16878,7 @@
       <c r="AI53" s="110"/>
       <c r="AJ53" s="110"/>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A54" s="109">
         <f t="shared" si="17"/>
         <v>46</v>
@@ -16903,7 +16921,7 @@
       <c r="AI54" s="110"/>
       <c r="AJ54" s="110"/>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A55" s="109">
         <f t="shared" si="17"/>
         <v>47</v>
@@ -16946,7 +16964,7 @@
       <c r="AI55" s="110"/>
       <c r="AJ55" s="110"/>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A56" s="109">
         <f t="shared" si="17"/>
         <v>48</v>
@@ -16989,7 +17007,7 @@
       <c r="AI56" s="110"/>
       <c r="AJ56" s="110"/>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A57" s="109">
         <f t="shared" si="17"/>
         <v>49</v>
@@ -17032,7 +17050,7 @@
       <c r="AI57" s="110"/>
       <c r="AJ57" s="110"/>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A58" s="109">
         <f t="shared" si="17"/>
         <v>50</v>
@@ -17075,7 +17093,7 @@
       <c r="AI58" s="110"/>
       <c r="AJ58" s="110"/>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A59" s="109">
         <f t="shared" si="17"/>
         <v>51</v>
@@ -17118,7 +17136,7 @@
       <c r="AI59" s="110"/>
       <c r="AJ59" s="110"/>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A60" s="109">
         <f t="shared" si="17"/>
         <v>52</v>
@@ -17161,7 +17179,7 @@
       <c r="AI60" s="110"/>
       <c r="AJ60" s="110"/>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A61" s="109">
         <f t="shared" si="17"/>
         <v>53</v>
@@ -17204,7 +17222,7 @@
       <c r="AI61" s="110"/>
       <c r="AJ61" s="110"/>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A62" s="109">
         <f t="shared" si="17"/>
         <v>54</v>
@@ -17247,7 +17265,7 @@
       <c r="AI62" s="110"/>
       <c r="AJ62" s="110"/>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A63" s="109">
         <f t="shared" si="17"/>
         <v>55</v>
@@ -17290,7 +17308,7 @@
       <c r="AI63" s="110"/>
       <c r="AJ63" s="110"/>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A64" s="109">
         <f t="shared" si="17"/>
         <v>56</v>
@@ -17333,7 +17351,7 @@
       <c r="AI64" s="110"/>
       <c r="AJ64" s="110"/>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A65" s="109">
         <f t="shared" si="17"/>
         <v>57</v>
@@ -17400,7 +17418,7 @@
       <c r="AI65" s="110"/>
       <c r="AJ65" s="110"/>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A66" s="109">
         <f t="shared" si="17"/>
         <v>58</v>
@@ -17443,7 +17461,7 @@
       <c r="AI66" s="110"/>
       <c r="AJ66" s="110"/>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A67" s="109">
         <f t="shared" si="17"/>
         <v>59</v>
@@ -17486,7 +17504,7 @@
       <c r="AI67" s="110"/>
       <c r="AJ67" s="110"/>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A68" s="109">
         <f t="shared" si="17"/>
         <v>60</v>
@@ -17529,7 +17547,7 @@
       <c r="AI68" s="110"/>
       <c r="AJ68" s="110"/>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A69" s="109">
         <f t="shared" si="17"/>
         <v>61</v>
@@ -17572,7 +17590,7 @@
       <c r="AI69" s="110"/>
       <c r="AJ69" s="110"/>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A70" s="109">
         <f t="shared" si="17"/>
         <v>62</v>
@@ -17615,7 +17633,7 @@
       <c r="AI70" s="110"/>
       <c r="AJ70" s="110"/>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A71" s="109">
         <f t="shared" si="17"/>
         <v>63</v>
@@ -17658,7 +17676,7 @@
       <c r="AI71" s="110"/>
       <c r="AJ71" s="110"/>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A72" s="109">
         <f t="shared" si="17"/>
         <v>64</v>
@@ -17701,7 +17719,7 @@
       <c r="AI72" s="110"/>
       <c r="AJ72" s="110"/>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A73" s="109">
         <f t="shared" si="17"/>
         <v>65</v>
@@ -17744,7 +17762,7 @@
       <c r="AI73" s="110"/>
       <c r="AJ73" s="110"/>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A74" s="109">
         <f t="shared" si="17"/>
         <v>66</v>
@@ -17787,7 +17805,7 @@
       <c r="AI74" s="110"/>
       <c r="AJ74" s="110"/>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A75" s="109">
         <f t="shared" si="17"/>
         <v>67</v>
@@ -17830,7 +17848,7 @@
       <c r="AI75" s="110"/>
       <c r="AJ75" s="110"/>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A76" s="109">
         <f t="shared" si="17"/>
         <v>68</v>
@@ -17873,7 +17891,7 @@
       <c r="AI76" s="110"/>
       <c r="AJ76" s="110"/>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A77" s="109">
         <f t="shared" ref="A77:A80" si="38">+A76+1</f>
         <v>69</v>
@@ -17916,7 +17934,7 @@
       <c r="AI77" s="110"/>
       <c r="AJ77" s="110"/>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A78" s="109">
         <f t="shared" si="38"/>
         <v>70</v>
@@ -17959,7 +17977,7 @@
       <c r="AI78" s="110"/>
       <c r="AJ78" s="110"/>
     </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A79" s="109">
         <f t="shared" si="38"/>
         <v>71</v>
@@ -18002,7 +18020,7 @@
       <c r="AI79" s="110"/>
       <c r="AJ79" s="110"/>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A80" s="109">
         <f t="shared" si="38"/>
         <v>72</v>
@@ -18040,7 +18058,7 @@
       <c r="AI80" s="110"/>
       <c r="AJ80" s="110"/>
     </row>
-    <row r="81" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:36" x14ac:dyDescent="0.2">
       <c r="H81" s="110"/>
       <c r="I81" s="110"/>
       <c r="J81" s="110"/>
@@ -18071,7 +18089,7 @@
       <c r="AI81" s="110"/>
       <c r="AJ81" s="110"/>
     </row>
-    <row r="82" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:36" x14ac:dyDescent="0.2">
       <c r="H82" s="110"/>
       <c r="I82" s="110"/>
       <c r="J82" s="110"/>
@@ -18102,22 +18120,22 @@
       <c r="AI82" s="110"/>
       <c r="AJ82" s="110"/>
     </row>
-    <row r="83" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH83" s="110"/>
       <c r="AI83" s="110"/>
       <c r="AJ83" s="110"/>
     </row>
-    <row r="84" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH84" s="110"/>
       <c r="AI84" s="110"/>
       <c r="AJ84" s="110"/>
     </row>
-    <row r="85" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH85" s="110"/>
       <c r="AI85" s="110"/>
       <c r="AJ85" s="110"/>
     </row>
-    <row r="86" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A86" s="109">
         <f>+A10+1</f>
         <v>3</v>
@@ -18204,7 +18222,7 @@
       <c r="AI86" s="110"/>
       <c r="AJ86" s="110"/>
     </row>
-    <row r="87" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A87" s="109">
         <f>+A86+1</f>
         <v>4</v>
@@ -18284,7 +18302,7 @@
       <c r="AI87" s="110"/>
       <c r="AJ87" s="110"/>
     </row>
-    <row r="88" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A88" s="109">
         <f>+A87+1</f>
         <v>5</v>
@@ -18372,237 +18390,237 @@
       <c r="AI88" s="110"/>
       <c r="AJ88" s="110"/>
     </row>
-    <row r="89" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH89" s="110"/>
       <c r="AI89" s="110"/>
       <c r="AJ89" s="110"/>
     </row>
-    <row r="90" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH90" s="110"/>
       <c r="AI90" s="110"/>
       <c r="AJ90" s="110"/>
     </row>
-    <row r="91" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH91" s="110"/>
       <c r="AI91" s="110"/>
       <c r="AJ91" s="110"/>
     </row>
-    <row r="92" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH92" s="110"/>
       <c r="AI92" s="110"/>
       <c r="AJ92" s="110"/>
     </row>
-    <row r="93" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH93" s="110"/>
       <c r="AI93" s="110"/>
       <c r="AJ93" s="110"/>
     </row>
-    <row r="94" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH94" s="110"/>
       <c r="AI94" s="110"/>
       <c r="AJ94" s="110"/>
     </row>
-    <row r="95" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH95" s="110"/>
       <c r="AI95" s="110"/>
       <c r="AJ95" s="110"/>
     </row>
-    <row r="96" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:36" x14ac:dyDescent="0.2">
       <c r="AH96" s="110"/>
       <c r="AI96" s="110"/>
       <c r="AJ96" s="110"/>
     </row>
-    <row r="97" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="97" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH97" s="110"/>
       <c r="AI97" s="110"/>
       <c r="AJ97" s="110"/>
     </row>
-    <row r="98" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="98" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH98" s="110"/>
       <c r="AI98" s="110"/>
       <c r="AJ98" s="110"/>
     </row>
-    <row r="99" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="99" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH99" s="110"/>
       <c r="AI99" s="110"/>
       <c r="AJ99" s="110"/>
     </row>
-    <row r="100" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="100" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH100" s="110"/>
       <c r="AI100" s="110"/>
       <c r="AJ100" s="110"/>
     </row>
-    <row r="101" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="101" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH101" s="110"/>
       <c r="AI101" s="110"/>
       <c r="AJ101" s="110"/>
     </row>
-    <row r="102" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="102" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH102" s="110"/>
       <c r="AI102" s="110"/>
       <c r="AJ102" s="110"/>
     </row>
-    <row r="103" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="103" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH103" s="110"/>
       <c r="AI103" s="110"/>
       <c r="AJ103" s="110"/>
     </row>
-    <row r="104" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="104" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH104" s="110"/>
       <c r="AI104" s="110"/>
       <c r="AJ104" s="110"/>
     </row>
-    <row r="105" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="105" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH105" s="110"/>
       <c r="AI105" s="110"/>
       <c r="AJ105" s="110"/>
     </row>
-    <row r="106" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="106" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH106" s="110"/>
       <c r="AI106" s="110"/>
       <c r="AJ106" s="110"/>
     </row>
-    <row r="107" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="107" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH107" s="110"/>
       <c r="AI107" s="110"/>
       <c r="AJ107" s="110"/>
     </row>
-    <row r="108" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="108" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH108" s="110"/>
       <c r="AI108" s="110"/>
       <c r="AJ108" s="110"/>
     </row>
-    <row r="109" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="109" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH109" s="110"/>
       <c r="AI109" s="110"/>
       <c r="AJ109" s="110"/>
     </row>
-    <row r="110" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="110" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH110" s="110"/>
       <c r="AI110" s="110"/>
       <c r="AJ110" s="110"/>
     </row>
-    <row r="111" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="111" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH111" s="110"/>
       <c r="AI111" s="110"/>
       <c r="AJ111" s="110"/>
     </row>
-    <row r="112" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="112" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH112" s="110"/>
       <c r="AI112" s="110"/>
       <c r="AJ112" s="110"/>
     </row>
-    <row r="113" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="113" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH113" s="110"/>
       <c r="AI113" s="110"/>
       <c r="AJ113" s="110"/>
     </row>
-    <row r="114" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="114" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH114" s="110"/>
       <c r="AI114" s="110"/>
       <c r="AJ114" s="110"/>
     </row>
-    <row r="115" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="115" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH115" s="110"/>
       <c r="AI115" s="110"/>
       <c r="AJ115" s="110"/>
     </row>
-    <row r="116" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="116" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH116" s="110"/>
       <c r="AI116" s="110"/>
       <c r="AJ116" s="110"/>
     </row>
-    <row r="117" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="117" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH117" s="110"/>
       <c r="AI117" s="110"/>
       <c r="AJ117" s="110"/>
     </row>
-    <row r="118" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="118" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH118" s="110"/>
       <c r="AI118" s="110"/>
       <c r="AJ118" s="110"/>
     </row>
-    <row r="119" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="119" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH119" s="110"/>
       <c r="AI119" s="110"/>
       <c r="AJ119" s="110"/>
     </row>
-    <row r="120" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="120" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH120" s="110"/>
       <c r="AI120" s="110"/>
       <c r="AJ120" s="110"/>
     </row>
-    <row r="121" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="121" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH121" s="110"/>
       <c r="AI121" s="110"/>
       <c r="AJ121" s="110"/>
     </row>
-    <row r="122" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="122" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH122" s="110"/>
       <c r="AI122" s="110"/>
       <c r="AJ122" s="110"/>
     </row>
-    <row r="123" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="123" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH123" s="110"/>
       <c r="AI123" s="110"/>
       <c r="AJ123" s="110"/>
     </row>
-    <row r="124" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="124" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH124" s="110"/>
       <c r="AI124" s="110"/>
       <c r="AJ124" s="110"/>
     </row>
-    <row r="125" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="125" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH125" s="110"/>
       <c r="AI125" s="110"/>
       <c r="AJ125" s="110"/>
     </row>
-    <row r="126" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="126" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH126" s="110"/>
       <c r="AI126" s="110"/>
       <c r="AJ126" s="110"/>
     </row>
-    <row r="127" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="127" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH127" s="110"/>
       <c r="AI127" s="110"/>
       <c r="AJ127" s="110"/>
     </row>
-    <row r="128" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="128" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH128" s="110"/>
       <c r="AI128" s="110"/>
       <c r="AJ128" s="110"/>
     </row>
-    <row r="129" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="129" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH129" s="110"/>
       <c r="AI129" s="110"/>
       <c r="AJ129" s="110"/>
     </row>
-    <row r="130" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="130" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH130" s="110"/>
       <c r="AI130" s="110"/>
       <c r="AJ130" s="110"/>
     </row>
-    <row r="131" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="131" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH131" s="110"/>
       <c r="AI131" s="110"/>
       <c r="AJ131" s="110"/>
     </row>
-    <row r="132" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="132" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH132" s="110"/>
       <c r="AI132" s="110"/>
       <c r="AJ132" s="110"/>
     </row>
-    <row r="133" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="133" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH133" s="110"/>
       <c r="AI133" s="110"/>
       <c r="AJ133" s="110"/>
     </row>
-    <row r="134" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="134" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH134" s="110"/>
       <c r="AI134" s="110"/>
       <c r="AJ134" s="110"/>
     </row>
-    <row r="135" spans="34:36" x14ac:dyDescent="0.25">
+    <row r="135" spans="34:36" x14ac:dyDescent="0.2">
       <c r="AH135" s="110"/>
       <c r="AI135" s="110"/>
       <c r="AJ135" s="110"/>
@@ -18619,74 +18637,74 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57D91D0-A718-45C3-9EF2-C01D7940E5D3}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="87" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.453125" style="87" customWidth="1"/>
-    <col min="3" max="16384" width="9.1796875" style="87"/>
+    <col min="2" max="2" width="10.42578125" style="87" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="87"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="111" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="111" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" s="111" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="111" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="111" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="111" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="111"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="111"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="87" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" s="87" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B12" s="87" t="s">
         <v>342</v>
       </c>
@@ -18694,12 +18712,12 @@
         <v>343</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B13" s="87" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B14" s="109" t="s">
         <v>403</v>
       </c>
@@ -18707,7 +18725,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B15" s="109" t="s">
         <v>405</v>
       </c>
@@ -18723,26 +18741,26 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EE865A7-531A-484D-A1B8-5616406C41D1}">
   <dimension ref="A2:Y46"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" style="203" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" style="203" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" style="203" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="204" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" style="205" customWidth="1"/>
-    <col min="6" max="9" width="9.453125" style="202" customWidth="1"/>
-    <col min="10" max="10" width="10.453125" style="202" customWidth="1"/>
-    <col min="11" max="15" width="8.453125" style="206"/>
-    <col min="16" max="16" width="8.453125" style="211"/>
-    <col min="17" max="18" width="8.453125" style="206"/>
-    <col min="19" max="19" width="8.453125" style="212"/>
-    <col min="20" max="20" width="8.453125" style="211"/>
-    <col min="21" max="22" width="8.453125" style="206"/>
-    <col min="23" max="23" width="8.453125" style="212"/>
-    <col min="24" max="16384" width="8.453125" style="203"/>
+    <col min="1" max="1" width="4.85546875" style="203" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="203" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="203" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="204" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="205" customWidth="1"/>
+    <col min="6" max="9" width="9.42578125" style="202" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" style="202" customWidth="1"/>
+    <col min="11" max="15" width="8.42578125" style="206"/>
+    <col min="16" max="16" width="8.42578125" style="211"/>
+    <col min="17" max="18" width="8.42578125" style="206"/>
+    <col min="19" max="19" width="8.42578125" style="212"/>
+    <col min="20" max="20" width="8.42578125" style="211"/>
+    <col min="21" max="22" width="8.42578125" style="206"/>
+    <col min="23" max="23" width="8.42578125" style="212"/>
+    <col min="24" max="16384" width="8.42578125" style="203"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="L2" s="207">
         <f>AVERAGE(L4:L5)</f>
         <v>0.60998534549890704</v>
@@ -18764,7 +18782,7 @@
         <v>74.447011501450561</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B3" s="213" t="s">
         <v>0</v>
       </c>
@@ -18838,7 +18856,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="263" t="s">
         <v>251</v>
       </c>
@@ -18927,7 +18945,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="262" t="s">
         <v>251</v>
       </c>
@@ -19022,7 +19040,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="262" t="s">
         <v>251</v>
       </c>
@@ -19066,7 +19084,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="262"/>
       <c r="B7" s="80" t="s">
         <v>691</v>
@@ -19087,7 +19105,7 @@
       <c r="J7" s="222"/>
       <c r="O7" s="212"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="270" t="s">
         <v>251</v>
       </c>
@@ -19110,7 +19128,7 @@
       <c r="J8" s="222"/>
       <c r="O8" s="212"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="262" t="s">
         <v>251</v>
       </c>
@@ -19154,7 +19172,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="262" t="s">
         <v>251</v>
       </c>
@@ -19197,7 +19215,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="262" t="s">
         <v>251</v>
       </c>
@@ -19238,7 +19256,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="262" t="s">
         <v>251</v>
       </c>
@@ -19253,7 +19271,7 @@
       <c r="H12" s="205"/>
       <c r="O12" s="212"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="262" t="s">
         <v>251</v>
       </c>
@@ -19274,7 +19292,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="262" t="s">
         <v>251</v>
       </c>
@@ -19292,7 +19310,7 @@
       </c>
       <c r="O14" s="212"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="203" t="s">
         <v>251</v>
       </c>
@@ -19311,7 +19329,7 @@
       </c>
       <c r="O15" s="212"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="203" t="s">
         <v>251</v>
       </c>
@@ -19332,7 +19350,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="262" t="s">
         <v>251</v>
       </c>
@@ -19350,7 +19368,7 @@
       </c>
       <c r="O17" s="212"/>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="262" t="s">
         <v>251</v>
       </c>
@@ -19371,7 +19389,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B19" s="229" t="s">
         <v>101</v>
       </c>
@@ -19386,7 +19404,7 @@
       </c>
       <c r="O19" s="212"/>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B20" s="229" t="s">
         <v>105</v>
       </c>
@@ -19404,7 +19422,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B21" s="229" t="s">
         <v>109</v>
       </c>
@@ -19419,7 +19437,7 @@
       </c>
       <c r="O21" s="212"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B22" s="229" t="s">
         <v>113</v>
       </c>
@@ -19437,7 +19455,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="263" t="s">
         <v>251</v>
       </c>
@@ -19455,7 +19473,7 @@
       </c>
       <c r="O23" s="212"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="263" t="s">
         <v>251</v>
       </c>
@@ -19473,7 +19491,7 @@
       </c>
       <c r="O24" s="212"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B25" s="229" t="s">
         <v>121</v>
       </c>
@@ -19488,7 +19506,7 @@
       </c>
       <c r="O25" s="212"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="203" t="s">
         <v>251</v>
       </c>
@@ -19506,7 +19524,7 @@
       </c>
       <c r="O26" s="212"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="203" t="s">
         <v>251</v>
       </c>
@@ -19524,7 +19542,7 @@
       </c>
       <c r="O27" s="212"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B28" s="229" t="s">
         <v>133</v>
       </c>
@@ -19539,7 +19557,7 @@
       </c>
       <c r="O28" s="212"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="203" t="s">
         <v>251</v>
       </c>
@@ -19557,7 +19575,7 @@
       </c>
       <c r="O29" s="212"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="263" t="s">
         <v>251</v>
       </c>
@@ -19575,7 +19593,7 @@
       </c>
       <c r="O30" s="212"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B31" s="80" t="s">
         <v>330</v>
       </c>
@@ -19609,7 +19627,7 @@
       </c>
       <c r="O31" s="212"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A32" s="203" t="s">
         <v>251</v>
       </c>
@@ -19621,7 +19639,7 @@
       </c>
       <c r="O32" s="212"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="203" t="s">
         <v>251</v>
       </c>
@@ -19639,7 +19657,7 @@
       </c>
       <c r="O33" s="212"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B34" s="229" t="s">
         <v>213</v>
       </c>
@@ -19654,7 +19672,7 @@
       </c>
       <c r="O34" s="212"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B35" s="229" t="s">
         <v>215</v>
       </c>
@@ -19669,7 +19687,7 @@
       </c>
       <c r="O35" s="212"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B36" s="229" t="s">
         <v>224</v>
       </c>
@@ -19678,13 +19696,13 @@
       </c>
       <c r="O36" s="212"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B37" s="229" t="s">
         <v>389</v>
       </c>
       <c r="O37" s="212"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="203" t="s">
         <v>251</v>
       </c>
@@ -19696,7 +19714,7 @@
       </c>
       <c r="O38" s="212"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B39" s="335" t="s">
         <v>732</v>
       </c>
@@ -19708,7 +19726,7 @@
       </c>
       <c r="O39" s="212"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="203" t="s">
         <v>251</v>
       </c>
@@ -19720,7 +19738,7 @@
       </c>
       <c r="O40" s="212"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="203" t="s">
         <v>251</v>
       </c>
@@ -19732,7 +19750,7 @@
       </c>
       <c r="O41" s="212"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B42" s="229" t="s">
         <v>631</v>
       </c>
@@ -19741,7 +19759,7 @@
       </c>
       <c r="O42" s="212"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="203" t="s">
         <v>251</v>
       </c>
@@ -19753,7 +19771,7 @@
       </c>
       <c r="O43" s="212"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="203" t="s">
         <v>251</v>
       </c>
@@ -19765,7 +19783,7 @@
       </c>
       <c r="O44" s="212"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="203" t="s">
         <v>251</v>
       </c>
@@ -19777,7 +19795,7 @@
       </c>
       <c r="O45" s="212"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="203" t="s">
         <v>251</v>
       </c>
@@ -19821,21 +19839,22 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972A0FE3-503A-448B-BE6E-F545711F1B98}">
   <dimension ref="A1:X79"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" style="54" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" style="54" customWidth="1"/>
     <col min="3" max="3" width="11" style="54" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="54"/>
+    <col min="4" max="4" width="9.140625" style="54"/>
     <col min="5" max="5" width="10" style="54" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="54"/>
-    <col min="7" max="7" width="10.1796875" style="54" customWidth="1"/>
-    <col min="8" max="9" width="9.1796875" style="54"/>
-    <col min="10" max="10" width="10.81640625" style="54" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="54"/>
+    <col min="6" max="6" width="9.140625" style="54"/>
+    <col min="7" max="7" width="10.140625" style="54" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="54"/>
+    <col min="10" max="10" width="10.85546875" style="54" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
@@ -19843,7 +19862,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B2" s="55" t="s">
         <v>0</v>
       </c>
@@ -19914,7 +19933,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="262" t="s">
         <v>251</v>
       </c>
@@ -20005,7 +20024,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="4" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="264" t="s">
         <v>251</v>
       </c>
@@ -20057,7 +20076,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="264" t="s">
         <v>251</v>
       </c>
@@ -20075,15 +20094,15 @@
         <v>412077.53318192996</v>
       </c>
       <c r="F5" s="22">
-        <f>[12]Main!$L$5-[12]Main!$L$6</f>
+        <f>[11]Main!$L$5-[11]Main!$L$6</f>
         <v>5430.6890000000003</v>
       </c>
       <c r="G5" s="22">
-        <f>E5-F5</f>
+        <f t="shared" ref="G5:G14" si="0">E5-F5</f>
         <v>406646.84418192995</v>
       </c>
       <c r="H5" s="22">
-        <f>+[12]Main!$L$3</f>
+        <f>+[11]Main!$L$3</f>
         <v>2358.9073969999999</v>
       </c>
       <c r="I5" s="245" t="s">
@@ -20093,7 +20112,7 @@
         <v>45692</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="264" t="s">
         <v>251</v>
       </c>
@@ -20111,15 +20130,15 @@
         <v>318354.5</v>
       </c>
       <c r="F6" s="22">
-        <f>+[11]Main!$L$5-[11]Main!$L$6</f>
+        <f>+[12]Main!$L$5-[12]Main!$L$6</f>
         <v>8195</v>
       </c>
       <c r="G6" s="22">
-        <f>E6-F6</f>
+        <f t="shared" si="0"/>
         <v>310159.5</v>
       </c>
       <c r="H6" s="22">
-        <f>+[11]Main!$L$3</f>
+        <f>+[12]Main!$L$3</f>
         <v>1178</v>
       </c>
       <c r="I6" s="248" t="s">
@@ -20145,7 +20164,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="264" t="s">
         <v>251</v>
       </c>
@@ -20163,15 +20182,15 @@
         <v>241886.40000000002</v>
       </c>
       <c r="F7" s="53">
-        <f>[14]Main!$M$5-[14]Main!$M$6</f>
+        <f>[13]Main!$M$5-[13]Main!$M$6</f>
         <v>-38732</v>
       </c>
       <c r="G7" s="22">
-        <f>E7-F7</f>
+        <f t="shared" si="0"/>
         <v>280618.40000000002</v>
       </c>
       <c r="H7" s="53">
-        <f>[14]Main!$M$3</f>
+        <f>[13]Main!$M$3</f>
         <v>920</v>
       </c>
       <c r="I7" s="161" t="s">
@@ -20184,7 +20203,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="264" t="s">
         <v>251</v>
       </c>
@@ -20198,19 +20217,19 @@
         <v>246.62</v>
       </c>
       <c r="E8" s="22">
-        <f>+D8*[13]Main!$M$3</f>
+        <f>+D8*[14]Main!$M$3</f>
         <v>239961.26</v>
       </c>
       <c r="F8" s="22">
-        <f>+[13]Main!$M$5-[13]Main!$M$6</f>
+        <f>+[14]Main!$M$5-[14]Main!$M$6</f>
         <v>17653</v>
       </c>
       <c r="G8" s="22">
-        <f>E8-F8</f>
+        <f t="shared" si="0"/>
         <v>222308.26</v>
       </c>
       <c r="H8" s="22">
-        <f>+[13]Main!$M$3</f>
+        <f>+[14]Main!$M$3</f>
         <v>973</v>
       </c>
       <c r="I8" s="143" t="s">
@@ -20220,7 +20239,7 @@
         <v>45555</v>
       </c>
       <c r="K8" s="27">
-        <f>+[13]Model!$AE$65</f>
+        <f>+[14]Model!$AE$65</f>
         <v>170.42672158668651</v>
       </c>
       <c r="L8" s="28">
@@ -20228,11 +20247,11 @@
         <v>-0.30895011926572657</v>
       </c>
       <c r="M8" s="28">
-        <f>+[13]Model!$AE$63</f>
+        <f>+[14]Model!$AE$63</f>
         <v>0.08</v>
       </c>
       <c r="N8" s="28">
-        <f>+[13]Model!$AE$62</f>
+        <f>+[14]Model!$AE$62</f>
         <v>0.01</v>
       </c>
       <c r="O8" s="28">
@@ -20250,7 +20269,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="264" t="s">
         <v>251</v>
       </c>
@@ -20272,7 +20291,7 @@
         <v>7397</v>
       </c>
       <c r="G9" s="22">
-        <f>E9-F9</f>
+        <f t="shared" si="0"/>
         <v>189984.6</v>
       </c>
       <c r="H9" s="22">
@@ -20302,7 +20321,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="264" t="s">
         <v>251</v>
       </c>
@@ -20316,19 +20335,19 @@
         <v>220.13</v>
       </c>
       <c r="E10" s="22">
-        <f>+D10*[18]Main!$M$3</f>
+        <f>+D10*[16]Main!$M$3</f>
         <v>72863.03</v>
       </c>
       <c r="F10" s="22">
-        <f>+[18]Main!$M$5-[18]Main!$M$6</f>
+        <f>+[16]Main!$M$5-[16]Main!$M$6</f>
         <v>5027.4579999999996</v>
       </c>
       <c r="G10" s="22">
-        <f>E10-F10</f>
+        <f t="shared" si="0"/>
         <v>67835.572</v>
       </c>
       <c r="H10" s="22">
-        <f>+[18]Main!$M$3</f>
+        <f>+[16]Main!$M$3</f>
         <v>331</v>
       </c>
       <c r="I10" s="34" t="s">
@@ -20341,7 +20360,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="264" t="s">
         <v>251</v>
       </c>
@@ -20359,15 +20378,15 @@
         <v>62455.200000000004</v>
       </c>
       <c r="F11" s="22">
-        <f>+[16]Main!$P$5-[16]Main!$P$6</f>
+        <f>+[17]Main!$P$5-[17]Main!$P$6</f>
         <v>4391</v>
       </c>
       <c r="G11" s="22">
-        <f>E11-F11</f>
+        <f t="shared" si="0"/>
         <v>58064.200000000004</v>
       </c>
       <c r="H11" s="23">
-        <f>+[16]Main!$P$3</f>
+        <f>+[17]Main!$P$3</f>
         <v>265</v>
       </c>
       <c r="I11" s="161" t="s">
@@ -20380,7 +20399,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="264" t="s">
         <v>251</v>
       </c>
@@ -20394,19 +20413,19 @@
         <v>170.87</v>
       </c>
       <c r="E12" s="22">
-        <f>+D12*[17]Main!$L$3</f>
+        <f>+D12*[18]Main!$L$3</f>
         <v>44426.200000000004</v>
       </c>
       <c r="F12" s="22">
-        <f>+[17]Main!$L$5-[17]Main!$L$6</f>
+        <f>+[18]Main!$L$5-[18]Main!$L$6</f>
         <v>1576</v>
       </c>
       <c r="G12" s="22">
-        <f>E12-F12</f>
+        <f t="shared" si="0"/>
         <v>42850.200000000004</v>
       </c>
       <c r="H12" s="22">
-        <f>+[17]Main!$L$3</f>
+        <f>+[18]Main!$L$3</f>
         <v>260</v>
       </c>
       <c r="I12" s="161" t="s">
@@ -20419,7 +20438,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="264" t="s">
         <v>251</v>
       </c>
@@ -20433,7 +20452,7 @@
         <v>136.93</v>
       </c>
       <c r="E13" s="22">
-        <f>+D13*H13</f>
+        <f t="shared" ref="E13:E19" si="1">+D13*H13</f>
         <v>46166.261015750009</v>
       </c>
       <c r="F13" s="53">
@@ -20441,7 +20460,7 @@
         <v>970</v>
       </c>
       <c r="G13" s="22">
-        <f>E13-F13</f>
+        <f t="shared" si="0"/>
         <v>45196.261015750009</v>
       </c>
       <c r="H13" s="53">
@@ -20458,7 +20477,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="264" t="s">
         <v>251</v>
       </c>
@@ -20472,7 +20491,7 @@
         <v>279.26</v>
       </c>
       <c r="E14" s="22">
-        <f>+D14*H14</f>
+        <f t="shared" si="1"/>
         <v>43242.5746163</v>
       </c>
       <c r="F14" s="22">
@@ -20480,7 +20499,7 @@
         <v>2838.5529999999999</v>
       </c>
       <c r="G14" s="22">
-        <f>E14-F14</f>
+        <f t="shared" si="0"/>
         <v>40404.0216163</v>
       </c>
       <c r="H14" s="22">
@@ -20497,7 +20516,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="264" t="s">
         <v>251</v>
       </c>
@@ -20511,7 +20530,7 @@
         <v>519.58000000000004</v>
       </c>
       <c r="E15" s="146">
-        <f>+D15*H15</f>
+        <f t="shared" si="1"/>
         <v>26679.829248040001</v>
       </c>
       <c r="F15" s="22">
@@ -20549,7 +20568,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="264" t="s">
         <v>251</v>
       </c>
@@ -20560,11 +20579,11 @@
         <v>183</v>
       </c>
       <c r="D16" s="21">
-        <v>315.52</v>
+        <v>359.82</v>
       </c>
       <c r="E16" s="22">
-        <f>+D16*H16</f>
-        <v>23348.48</v>
+        <f t="shared" si="1"/>
+        <v>29274.9552</v>
       </c>
       <c r="F16" s="22">
         <f>+[22]Main!$J$5-[22]Main!$J$6</f>
@@ -20572,21 +20591,30 @@
       </c>
       <c r="G16" s="22">
         <f>+E16-F16</f>
-        <v>22171.48</v>
+        <v>28097.9552</v>
       </c>
       <c r="H16" s="22">
         <f>+[22]Main!$J$3</f>
-        <v>74</v>
-      </c>
-      <c r="I16" s="202" t="s">
-        <v>651</v>
+        <v>81.36</v>
+      </c>
+      <c r="I16" s="334" t="s">
+        <v>771</v>
       </c>
       <c r="J16" s="37">
-        <v>45636</v>
-      </c>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
+        <v>45869</v>
+      </c>
+      <c r="K16" s="342">
+        <f>[22]Model!$AC$47</f>
+        <v>607.75128881946102</v>
+      </c>
+      <c r="L16" s="28">
+        <f>+K16/D16-1</f>
+        <v>0.68904254577138868</v>
+      </c>
+      <c r="M16" s="28">
+        <f>[22]Model!$AC$44</f>
+        <v>0.11</v>
+      </c>
       <c r="N16" s="24"/>
       <c r="O16" s="26"/>
       <c r="P16" s="25"/>
@@ -20601,7 +20629,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="125" t="s">
         <v>251</v>
       </c>
@@ -20615,7 +20643,7 @@
         <v>77.08</v>
       </c>
       <c r="E17" s="22">
-        <f>+D17*H17</f>
+        <f t="shared" si="1"/>
         <v>11586.475674879999</v>
       </c>
       <c r="F17" s="53">
@@ -20637,7 +20665,7 @@
         <v>45719</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="264" t="s">
         <v>251</v>
       </c>
@@ -20651,7 +20679,7 @@
         <v>92.26</v>
       </c>
       <c r="E18" s="22">
-        <f>+D18*H18</f>
+        <f t="shared" si="1"/>
         <v>15671.47328656</v>
       </c>
       <c r="F18" s="22">
@@ -20689,7 +20717,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="264" t="s">
         <v>251</v>
       </c>
@@ -20703,7 +20731,7 @@
         <v>86.53</v>
       </c>
       <c r="E19" s="22">
-        <f>+D19*H19</f>
+        <f t="shared" si="1"/>
         <v>26633.00077395</v>
       </c>
       <c r="F19" s="22">
@@ -20728,7 +20756,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="125" t="s">
         <v>251</v>
       </c>
@@ -20766,7 +20794,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="264" t="s">
         <v>251</v>
       </c>
@@ -20815,7 +20843,7 @@
       <c r="V21" s="24"/>
       <c r="W21" s="24"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="125" t="s">
         <v>251</v>
       </c>
@@ -20832,7 +20860,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="125" t="s">
         <v>251</v>
       </c>
@@ -20849,7 +20877,7 @@
         <v>12660</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="125" t="s">
         <v>251</v>
       </c>
@@ -20866,7 +20894,7 @@
         <v>12990</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="125" t="s">
         <v>251</v>
       </c>
@@ -20883,7 +20911,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A26" s="264" t="s">
         <v>251</v>
       </c>
@@ -20903,7 +20931,7 @@
       <c r="I26" s="23"/>
       <c r="J26" s="74"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="322" t="s">
         <v>251</v>
       </c>
@@ -20925,7 +20953,7 @@
       <c r="I27" s="23"/>
       <c r="J27" s="74"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="125" t="s">
         <v>251</v>
       </c>
@@ -20943,7 +20971,7 @@
       <c r="I28" s="73"/>
       <c r="J28" s="74"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A29" s="264" t="s">
         <v>251</v>
       </c>
@@ -20960,7 +20988,7 @@
         <v>10300</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="125" t="s">
         <v>251</v>
       </c>
@@ -20973,7 +21001,7 @@
       <c r="D30" s="21"/>
       <c r="E30" s="22"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="264" t="s">
         <v>251</v>
       </c>
@@ -20986,7 +21014,7 @@
       <c r="D31" s="21"/>
       <c r="E31" s="22"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B32" s="83" t="s">
         <v>111</v>
       </c>
@@ -21000,7 +21028,7 @@
         <v>9140</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A33" s="125" t="s">
         <v>251</v>
       </c>
@@ -21013,7 +21041,7 @@
       <c r="D33" s="21"/>
       <c r="E33" s="22"/>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="128" t="s">
         <v>251</v>
       </c>
@@ -21026,7 +21054,7 @@
       <c r="D34" s="21"/>
       <c r="E34" s="22"/>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="125" t="s">
         <v>251</v>
       </c>
@@ -21039,7 +21067,7 @@
       <c r="D35" s="21"/>
       <c r="E35" s="22"/>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="264" t="s">
         <v>251</v>
       </c>
@@ -21056,7 +21084,7 @@
         <v>16020</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="264" t="s">
         <v>251</v>
       </c>
@@ -21069,7 +21097,7 @@
       <c r="D37" s="21"/>
       <c r="E37" s="22"/>
     </row>
-    <row r="38" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="125" t="s">
         <v>251</v>
       </c>
@@ -21107,7 +21135,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="125" t="s">
         <v>251</v>
       </c>
@@ -21138,7 +21166,7 @@
       <c r="V39" s="24"/>
       <c r="W39" s="24"/>
     </row>
-    <row r="40" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="125" t="s">
         <v>251</v>
       </c>
@@ -21169,7 +21197,7 @@
       <c r="V40" s="24"/>
       <c r="W40" s="24"/>
     </row>
-    <row r="41" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="128" t="s">
         <v>251</v>
       </c>
@@ -21218,7 +21246,7 @@
       <c r="V41" s="24"/>
       <c r="W41" s="24"/>
     </row>
-    <row r="42" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="128" t="s">
         <v>251</v>
       </c>
@@ -21267,7 +21295,7 @@
       <c r="V42" s="24"/>
       <c r="W42" s="24"/>
     </row>
-    <row r="43" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="128" t="s">
         <v>251</v>
       </c>
@@ -21316,7 +21344,7 @@
       <c r="V43" s="24"/>
       <c r="W43" s="24"/>
     </row>
-    <row r="44" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="125"/>
       <c r="B44" s="5" t="s">
         <v>687</v>
@@ -21363,7 +21391,7 @@
       <c r="V44" s="24"/>
       <c r="W44" s="24"/>
     </row>
-    <row r="45" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="125"/>
       <c r="B45" s="5" t="s">
         <v>611</v>
@@ -21410,7 +21438,7 @@
       <c r="V45" s="24"/>
       <c r="W45" s="24"/>
     </row>
-    <row r="46" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="125" t="s">
         <v>251</v>
       </c>
@@ -21441,7 +21469,7 @@
       <c r="V46" s="24"/>
       <c r="W46" s="24"/>
     </row>
-    <row r="47" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="125" t="s">
         <v>251</v>
       </c>
@@ -21472,7 +21500,7 @@
       <c r="V47" s="24"/>
       <c r="W47" s="24"/>
     </row>
-    <row r="48" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="125" t="s">
         <v>251</v>
       </c>
@@ -21503,7 +21531,7 @@
       <c r="V48" s="24"/>
       <c r="W48" s="24"/>
     </row>
-    <row r="49" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="125" t="s">
         <v>251</v>
       </c>
@@ -21534,7 +21562,7 @@
       <c r="V49" s="24"/>
       <c r="W49" s="24"/>
     </row>
-    <row r="50" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="125" t="s">
         <v>251</v>
       </c>
@@ -21565,7 +21593,7 @@
       <c r="V50" s="24"/>
       <c r="W50" s="24"/>
     </row>
-    <row r="51" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="125" t="s">
         <v>251</v>
       </c>
@@ -21596,7 +21624,7 @@
       <c r="V51" s="24"/>
       <c r="W51" s="24"/>
     </row>
-    <row r="52" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="125" t="s">
         <v>251</v>
       </c>
@@ -21627,7 +21655,7 @@
       <c r="V52" s="24"/>
       <c r="W52" s="24"/>
     </row>
-    <row r="53" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="125" t="s">
         <v>251</v>
       </c>
@@ -21658,7 +21686,7 @@
       <c r="V53" s="24"/>
       <c r="W53" s="24"/>
     </row>
-    <row r="54" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="127" t="s">
         <v>251</v>
       </c>
@@ -21691,7 +21719,7 @@
       <c r="V54" s="24"/>
       <c r="W54" s="24"/>
     </row>
-    <row r="55" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="127" t="s">
         <v>251</v>
       </c>
@@ -21722,7 +21750,7 @@
       <c r="V55" s="24"/>
       <c r="W55" s="24"/>
     </row>
-    <row r="56" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="128" t="s">
         <v>251</v>
       </c>
@@ -21753,7 +21781,7 @@
       <c r="V56" s="24"/>
       <c r="W56" s="24"/>
     </row>
-    <row r="57" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" s="128" t="s">
         <v>251</v>
       </c>
@@ -21784,7 +21812,7 @@
       <c r="V57" s="24"/>
       <c r="W57" s="24"/>
     </row>
-    <row r="58" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="128" t="s">
         <v>251</v>
       </c>
@@ -21815,7 +21843,7 @@
       <c r="V58" s="24"/>
       <c r="W58" s="24"/>
     </row>
-    <row r="59" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="128" t="s">
         <v>251</v>
       </c>
@@ -21846,7 +21874,7 @@
       <c r="V59" s="24"/>
       <c r="W59" s="24"/>
     </row>
-    <row r="60" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="128" t="s">
         <v>251</v>
       </c>
@@ -21877,7 +21905,7 @@
       <c r="V60" s="24"/>
       <c r="W60" s="24"/>
     </row>
-    <row r="61" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="128" t="s">
         <v>251</v>
       </c>
@@ -21908,7 +21936,7 @@
       <c r="V61" s="24"/>
       <c r="W61" s="24"/>
     </row>
-    <row r="62" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="128" t="s">
         <v>251</v>
       </c>
@@ -21939,7 +21967,7 @@
       <c r="V62" s="24"/>
       <c r="W62" s="24"/>
     </row>
-    <row r="63" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="128" t="s">
         <v>251</v>
       </c>
@@ -21970,7 +21998,7 @@
       <c r="V63" s="24"/>
       <c r="W63" s="24"/>
     </row>
-    <row r="64" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="128"/>
       <c r="B64" s="5" t="s">
         <v>616</v>
@@ -22017,7 +22045,7 @@
       <c r="V64" s="24"/>
       <c r="W64" s="24"/>
     </row>
-    <row r="65" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="128" t="s">
         <v>251</v>
       </c>
@@ -22048,7 +22076,7 @@
       <c r="V65" s="24"/>
       <c r="W65" s="24"/>
     </row>
-    <row r="66" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="128" t="s">
         <v>251</v>
       </c>
@@ -22079,7 +22107,7 @@
       <c r="V66" s="24"/>
       <c r="W66" s="24"/>
     </row>
-    <row r="67" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="128" t="s">
         <v>251</v>
       </c>
@@ -22110,7 +22138,7 @@
       <c r="V67" s="24"/>
       <c r="W67" s="24"/>
     </row>
-    <row r="68" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="128" t="s">
         <v>251</v>
       </c>
@@ -22141,7 +22169,7 @@
       <c r="V68" s="24"/>
       <c r="W68" s="24"/>
     </row>
-    <row r="69" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="128" t="s">
         <v>251</v>
       </c>
@@ -22172,7 +22200,7 @@
       <c r="V69" s="24"/>
       <c r="W69" s="24"/>
     </row>
-    <row r="70" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="128"/>
       <c r="B70" s="203" t="s">
         <v>653</v>
@@ -22201,7 +22229,7 @@
       <c r="V70" s="24"/>
       <c r="W70" s="24"/>
     </row>
-    <row r="71" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="128"/>
       <c r="B71" s="240" t="s">
         <v>660</v>
@@ -22232,7 +22260,7 @@
       <c r="V71" s="24"/>
       <c r="W71" s="24"/>
     </row>
-    <row r="72" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="128"/>
       <c r="B72" s="5" t="s">
         <v>663</v>
@@ -22276,7 +22304,7 @@
       <c r="V72" s="24"/>
       <c r="W72" s="24"/>
     </row>
-    <row r="73" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="127"/>
       <c r="B73" s="127"/>
       <c r="C73" s="127"/>
@@ -22301,7 +22329,7 @@
       <c r="V73" s="24"/>
       <c r="W73" s="24"/>
     </row>
-    <row r="74" spans="1:23" ht="13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B74" s="69" t="s">
         <v>246</v>
       </c>
@@ -22309,7 +22337,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B75" s="103" t="s">
         <v>391</v>
       </c>
@@ -22320,7 +22348,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B76" s="103" t="s">
         <v>392</v>
       </c>
@@ -22340,7 +22368,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B77" s="103" t="s">
         <v>120</v>
       </c>
@@ -22351,7 +22379,7 @@
       <c r="G77" s="103"/>
       <c r="H77" s="103"/>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B78" s="117" t="s">
         <v>98</v>
       </c>
@@ -22359,7 +22387,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B79" s="68" t="s">
         <v>273</v>
       </c>
@@ -22404,26 +22432,26 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494F58CA-3A5E-4A8C-A323-FDAA45D59D23}">
   <dimension ref="A1:Z61"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="49" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="49" customWidth="1"/>
-    <col min="3" max="3" width="11.7265625" style="49" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="49"/>
-    <col min="5" max="5" width="9.453125" style="49" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" style="49"/>
-    <col min="7" max="7" width="9.453125" style="49" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.1796875" style="49"/>
-    <col min="10" max="10" width="10.81640625" style="49" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="49"/>
+    <col min="3" max="3" width="11.7109375" style="49" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="49"/>
+    <col min="5" max="5" width="9.42578125" style="49" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="49"/>
+    <col min="7" max="7" width="9.42578125" style="49" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="49"/>
+    <col min="10" max="10" width="10.85546875" style="49" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B2" s="13" t="s">
         <v>0</v>
       </c>
@@ -22500,7 +22528,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="3" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="262" t="s">
         <v>251</v>
       </c>
@@ -22571,7 +22599,7 @@
         <v>386.61436855118114</v>
       </c>
     </row>
-    <row r="4" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="262" t="s">
         <v>251</v>
       </c>
@@ -22623,7 +22651,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="262" t="s">
         <v>251</v>
       </c>
@@ -22657,7 +22685,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="6" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="262" t="s">
         <v>251</v>
       </c>
@@ -22691,7 +22719,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="262" t="s">
         <v>251</v>
       </c>
@@ -22732,7 +22760,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="90"/>
       <c r="B8" s="89" t="s">
         <v>371</v>
@@ -22786,7 +22814,7 @@
         <v>51.220903999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="262" t="s">
         <v>251</v>
       </c>
@@ -22820,7 +22848,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="70" t="s">
         <v>280</v>
       </c>
@@ -22851,7 +22879,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="262" t="s">
         <v>251</v>
       </c>
@@ -22900,7 +22928,7 @@
       <c r="V11" s="24"/>
       <c r="W11" s="24"/>
     </row>
-    <row r="12" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B12" s="84" t="s">
         <v>316</v>
       </c>
@@ -22928,7 +22956,7 @@
       <c r="V12" s="24"/>
       <c r="W12" s="24"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="262" t="s">
         <v>251</v>
       </c>
@@ -22964,7 +22992,7 @@
         <v>45601</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="83" t="s">
         <v>129</v>
       </c>
@@ -22996,7 +23024,7 @@
       <c r="V14" s="24"/>
       <c r="W14" s="26"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B15" s="84" t="s">
         <v>321</v>
       </c>
@@ -23010,7 +23038,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="16" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
         <v>355</v>
       </c>
@@ -23059,7 +23087,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
         <v>635</v>
       </c>
@@ -23092,7 +23120,7 @@
         <v>45575</v>
       </c>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B18" s="5" t="s">
         <v>661</v>
       </c>
@@ -23109,7 +23137,7 @@
       <c r="I18" s="189"/>
       <c r="J18" s="187"/>
     </row>
-    <row r="19" spans="2:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B19" s="132" t="s">
         <v>613</v>
       </c>
@@ -23135,7 +23163,7 @@
       <c r="V19" s="24"/>
       <c r="W19" s="24"/>
     </row>
-    <row r="20" spans="2:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="132" t="s">
         <v>614</v>
       </c>
@@ -23161,7 +23189,7 @@
       <c r="V20" s="24"/>
       <c r="W20" s="24"/>
     </row>
-    <row r="21" spans="2:23" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:23" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B21" s="5"/>
       <c r="D21" s="21"/>
       <c r="E21" s="22"/>
@@ -23184,7 +23212,7 @@
       <c r="V21" s="24"/>
       <c r="W21" s="24"/>
     </row>
-    <row r="22" spans="2:23" ht="13" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B22" s="50" t="s">
         <v>246</v>
       </c>
@@ -23192,7 +23220,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B23" s="70" t="s">
         <v>275</v>
       </c>
@@ -23200,7 +23228,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B24" s="49" t="s">
         <v>245</v>
       </c>
@@ -23208,7 +23236,7 @@
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B25" s="142" t="s">
         <v>620</v>
       </c>
@@ -23222,7 +23250,7 @@
         <v>34050</v>
       </c>
     </row>
-    <row r="26" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B26" s="84" t="s">
         <v>315</v>
       </c>
@@ -23236,7 +23264,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B27" s="118" t="s">
         <v>441</v>
       </c>
@@ -23248,7 +23276,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B28" s="118" t="s">
         <v>442</v>
       </c>
@@ -23259,7 +23287,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B29" s="49" t="s">
         <v>244</v>
       </c>
@@ -23267,162 +23295,162 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B30" s="84" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B31" s="84" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B32" s="84" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B33" s="84" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" s="84" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" s="88" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B36" s="49" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B37" s="88" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B38" s="108" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B39" s="88" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B40" s="88" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B41" s="88" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B42" s="88" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B43" s="88" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B44" s="88" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B45" s="88" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B46" s="88" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B47" s="88" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B48" s="88" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" s="88" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B50" s="88" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B51" s="88" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B52" s="88" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B53" s="88" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B54" s="88" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B55" s="88" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B56" s="88" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B57" s="88" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B58" s="88" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B59" s="142" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B60" s="142" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B61" s="142" t="s">
         <v>623</v>
       </c>
@@ -23448,19 +23476,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4F12437-B4E9-44AF-8552-EF0FF979C92B}">
   <dimension ref="A1:X28"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" style="148" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="148" customWidth="1"/>
-    <col min="3" max="16384" width="9.1796875" style="148"/>
+    <col min="3" max="16384" width="9.140625" style="148"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="148" t="s">
         <v>0</v>
@@ -23490,7 +23518,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="267" t="s">
         <v>251</v>
       </c>
@@ -23539,7 +23567,7 @@
       <c r="V3" s="153"/>
       <c r="W3" s="155"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="267" t="s">
         <v>251</v>
       </c>
@@ -23583,7 +23611,7 @@
       <c r="V4" s="153"/>
       <c r="W4" s="155"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="267" t="s">
         <v>251</v>
       </c>
@@ -23630,7 +23658,7 @@
       <c r="V5" s="153"/>
       <c r="W5" s="155"/>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="267" t="s">
         <v>251</v>
       </c>
@@ -23680,7 +23708,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="267" t="s">
         <v>251</v>
       </c>
@@ -23729,7 +23757,7 @@
       <c r="V7" s="153"/>
       <c r="W7" s="155"/>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="267" t="s">
         <v>251</v>
       </c>
@@ -23781,7 +23809,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="148" t="s">
         <v>251</v>
       </c>
@@ -23798,7 +23826,7 @@
         <v>13640</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B10" s="148" t="s">
         <v>220</v>
       </c>
@@ -23830,7 +23858,7 @@
       <c r="V10" s="153"/>
       <c r="W10" s="155"/>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B11" s="148" t="s">
         <v>313</v>
       </c>
@@ -23845,7 +23873,7 @@
       <c r="I11" s="149"/>
       <c r="J11" s="149"/>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B12" s="148" t="s">
         <v>314</v>
       </c>
@@ -23857,7 +23885,7 @@
       <c r="I12" s="149"/>
       <c r="J12" s="149"/>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="267" t="s">
         <v>251</v>
       </c>
@@ -23868,7 +23896,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="148" t="s">
         <v>251</v>
       </c>
@@ -23885,7 +23913,7 @@
         <v>13880</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="148" t="s">
         <v>251</v>
       </c>
@@ -23896,7 +23924,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="148" t="s">
         <v>251</v>
       </c>
@@ -23907,7 +23935,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="148" t="s">
         <v>251</v>
       </c>
@@ -23918,7 +23946,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="148" t="s">
         <v>251</v>
       </c>
@@ -23929,7 +23957,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="148" t="s">
         <v>251</v>
       </c>
@@ -23940,7 +23968,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="148" t="s">
         <v>251</v>
       </c>
@@ -23951,12 +23979,12 @@
         <v>555</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" s="69" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B23" s="148" t="s">
         <v>399</v>
       </c>
@@ -23964,7 +23992,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B24" s="148" t="s">
         <v>378</v>
       </c>
@@ -23972,7 +24000,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B25" s="148" t="s">
         <v>380</v>
       </c>
@@ -23980,7 +24008,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B26" s="148" t="s">
         <v>398</v>
       </c>
@@ -23988,12 +24016,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B27" s="148" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B28" s="148" t="s">
         <v>379</v>
       </c>
